--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -19,51 +19,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+  <x:si>
+    <x:t>item_chicken_salad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>훈련의 효율을 높여주는 음식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Single</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consumable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하위 단체 선수 등록에 필요한 자격증이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구급상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KeyItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>item_license_bronze</x:t>
+  </x:si>
   <x:si>
     <x:t>item_first_aid_kit</x:t>
   </x:si>
   <x:si>
-    <x:t>Consumable</x:t>
+    <x:t>부상 회복에 사용하는 아이템</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>브론즈 자격증</x:t>
   </x:si>
   <x:si>
-    <x:t>하위 단체 선수 등록에 필요한 자격증이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부상 회복에 사용하는 아이템</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구급상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KeyItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item_license_bronze</x:t>
+    <x:t>닭가슴살 샐러드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseTargetType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -852,69 +873,94 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4" ht="13.199999999999999">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>6</x:v>
+      <x:c r="E3" s="7" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A5" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A6" s="3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="B6" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="5"/>
+      <x:c r="E6" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A7" s="5"/>
